--- a/simulation_config.xlsx
+++ b/simulation_config.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation Config" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Simulation Config'!$A$1:$G$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Simulation Config'!$A$1:$G$258</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -169,7 +169,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -191,17 +191,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <right/>
-      <bottom style="thin">
-        <color rgb="00D5D8DC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -274,51 +268,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -687,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G212"/>
+  <dimension ref="A1:G224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -737,7 +686,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>📋 Simulation Settings</t>
         </is>
@@ -843,7 +792,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>📈 Economic Parameters</t>
         </is>
@@ -949,7 +898,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>🚧 Constraints</t>
         </is>
@@ -1024,7 +973,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>💰 Financial Parameters</t>
         </is>
@@ -1347,7 +1296,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>🌿 Natural Capital Debt (NCD)</t>
         </is>
@@ -1515,7 +1464,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>🌡️ Climate Parameters</t>
         </is>
@@ -1590,7 +1539,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>📊 Balance Sheet Parameters</t>
         </is>
@@ -1696,7 +1645,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="33" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>🔗 Contagion Engine</t>
         </is>
@@ -1802,7 +1751,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="34" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>💥 NPC Materiality Shocks</t>
         </is>
@@ -1900,7 +1849,7 @@
       <c r="G44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="35" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>⚙️ Engine Parameters</t>
         </is>
@@ -1948,4424 +1897,4462 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>synergy</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>max_reduction_per_round</t>
         </is>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="10" t="n">
         <v>0.06</v>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>F-06: hard ceiling on the synergy OPEX reduction per round</t>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>F-06: hard ceiling on the synergy OPEX reduction per round (default 0.06)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>natural_capital</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>interest_coefficient</t>
         </is>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="6" t="n">
         <v>0.0001</v>
       </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>rate/unit</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>NCD interest rate surcharge coefficient per unit NCD</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>natural_decay</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="10" t="n">
         <v>0.96</v>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>6-month passive decay multiplier for reputation/SLO scores</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>burnout</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>natural_drift</t>
         </is>
       </c>
-      <c r="D50" s="10" t="n">
+      <c r="D50" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>pts/round</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>Default passive burnout drift per round (no HR investment)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>burnout</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>opex_threshold</t>
         </is>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>Burnout level above which OPEX penalty activates</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>burnout</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>critical_threshold</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n">
+      <c r="D52" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>Burnout level classified as critical (amplified penalty)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>burnout</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>opex_penalty_coeff</t>
         </is>
       </c>
-      <c r="D53" s="6" t="n">
+      <c r="D53" s="10" t="n">
         <v>2.8125e-05</v>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>coeff</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>Quadratic coefficient for burnout → OPEX penalty curve</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>burnout</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>passive_decay_healthcare</t>
         </is>
       </c>
-      <c r="D54" s="10" t="n">
+      <c r="D54" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>pts/round</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>Healthcare BU burnout passive recovery per round</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>burnout</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>passive_decay_default</t>
         </is>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>pts/round</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G55" s="11" t="inlineStr">
         <is>
           <t>Non-healthcare BU burnout passive recovery per round</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>workforce_readiness</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>delta_high</t>
         </is>
       </c>
-      <c r="D56" s="10" t="n">
+      <c r="D56" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>Readiness boost from high HR investment</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>workforce_readiness</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>delta_medium</t>
         </is>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G57" s="11" t="inlineStr">
         <is>
           <t>Readiness boost from medium HR investment</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>workforce_readiness</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>delta_none</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n">
+      <c r="D58" s="6" t="n">
         <v>-10</v>
       </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>Readiness atrophy when no HR investment (negative)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>workforce_readiness</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>low_threshold</t>
         </is>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G59" s="11" t="inlineStr">
         <is>
           <t>Below this readiness → OPEX penalty applied</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>workforce_readiness</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>high_threshold</t>
         </is>
       </c>
-      <c r="D60" s="10" t="n">
+      <c r="D60" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>Above this readiness → OPEX bonus applied</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>talent_braindrain</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>reputation_threshold</t>
         </is>
       </c>
-      <c r="D61" s="6" t="n">
+      <c r="D61" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="G61" s="11" t="inlineStr">
         <is>
           <t>Reputation below this triggers brain-drain OPEX penalty</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>talent_braindrain</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>penalty_multiplier</t>
         </is>
       </c>
-      <c r="D62" s="10" t="n">
+      <c r="D62" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G62" s="11" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>OPEX penalty scaling multiplier for brain-drain</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>talent_braindrain</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>burnout_threshold</t>
         </is>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G63" s="11" t="inlineStr">
         <is>
           <t>Burnout above this triggers additional overhead cost</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>talent_braindrain</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>burnout_overhead_factor</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n">
+      <c r="D64" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G64" s="11" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>Overhead scaling factor when burnout exceeds threshold</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>overrun_risk</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>capex_threshold</t>
         </is>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="10" t="n">
         <v>3000000</v>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G65" s="11" t="inlineStr">
         <is>
           <t>CapEx above this → overrun risk probability activates</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>overrun_risk</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>default_probability</t>
         </is>
       </c>
-      <c r="D66" s="10" t="n">
+      <c r="D66" s="6" t="n">
         <v>0.25</v>
       </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>prob</t>
         </is>
       </c>
-      <c r="G66" s="11" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>Default probability of a cost overrun occurring</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>overrun_risk</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>default_severity</t>
         </is>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="G67" s="11" t="inlineStr">
         <is>
           <t>Default overrun cost as fraction of CapEx</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>technical_debt</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>rounds_threshold</t>
         </is>
       </c>
-      <c r="D68" s="10" t="n">
+      <c r="D68" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>rounds</t>
         </is>
       </c>
-      <c r="G68" s="11" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr">
         <is>
           <t>Consecutive zero-invest rounds before tech debt penalty</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>technical_debt</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>penalty_rate</t>
         </is>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="10" t="n">
         <v>0.04</v>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G69" s="11" t="inlineStr">
         <is>
           <t>OPEX penalty rate for accumulated technical debt</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>technology_lockin</t>
         </is>
       </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>rounds_threshold</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n">
+      <c r="D70" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E70" s="8" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>rounds</t>
         </is>
       </c>
-      <c r="G70" s="11" t="inlineStr">
+      <c r="G70" s="7" t="inlineStr">
         <is>
           <t>Consecutive rounds for technology lock-in trigger</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>technology_lockin</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>penalty_rate</t>
         </is>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
+      <c r="G71" s="11" t="inlineStr">
         <is>
           <t>Synergy penalty rate when technology lock-in fires</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>strike_probability</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>social_license_weight</t>
         </is>
       </c>
-      <c r="D72" s="10" t="n">
+      <c r="D72" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="G72" s="11" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>SLO deficit weight in strike probability calculation</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>cannibalization</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>base_rate</t>
         </is>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="D73" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G73" s="11" t="inlineStr">
         <is>
           <t>Base revenue cannibalization rate between overlapping BUs</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>cannibalization</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>aggressor_threshold_multiplier</t>
         </is>
       </c>
-      <c r="D74" s="10" t="n">
+      <c r="D74" s="6" t="n">
         <v>1.15</v>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
         <is>
           <t>Revenue multiple above avg that triggers aggressor status</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>dividend_ratchet</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>rep_penalty</t>
         </is>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G75" s="11" t="inlineStr">
         <is>
           <t>Reputation penalty when dividends are cut</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>dividend_ratchet</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>cut_threshold</t>
         </is>
       </c>
-      <c r="D76" s="10" t="n">
+      <c r="D76" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="G76" s="11" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>Dividend ratio below this vs. last round = 'cut'</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>talent_allocation</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>neglect_threshold</t>
         </is>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D77" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="G77" s="11" t="inlineStr">
         <is>
           <t>CapEx share below this → talent neglect penalty</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>talent_allocation</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>penalty_rate</t>
         </is>
       </c>
-      <c r="D78" s="10" t="n">
+      <c r="D78" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G78" s="11" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr">
         <is>
           <t>OPEX premium for talent neglect</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>stakeholder_fatigue</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="G79" s="11" t="inlineStr">
         <is>
           <t>Trust recovery fatigue factor (higher = slower recovery)</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>supply_chain</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>overlap_coefficient</t>
         </is>
       </c>
-      <c r="D80" s="10" t="n">
+      <c r="D80" s="6" t="n">
         <v>0.002</v>
       </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
       </c>
-      <c r="G80" s="11" t="inlineStr">
+      <c r="G80" s="7" t="inlineStr">
         <is>
           <t>Supply chain governance contagion rate between BUs</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>competitor</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>growth_rate</t>
         </is>
       </c>
-      <c r="D81" s="6" t="n">
+      <c r="D81" s="10" t="n">
         <v>0.06</v>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
         <is>
           <t>%/round</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr">
+      <c r="G81" s="11" t="inlineStr">
         <is>
           <t>NPC competitor EBITDA growth rate per round</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>greenwashing</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>investment_threshold</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n">
+      <c r="D82" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G82" s="11" t="inlineStr">
+      <c r="G82" s="7" t="inlineStr">
         <is>
           <t>Min investment ratio to back a green claim credibly</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>greenwashing</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>slo_penalty</t>
         </is>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D83" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr">
+      <c r="G83" s="11" t="inlineStr">
         <is>
           <t>SLO penalty per BU when greenwashing scandal fires</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>greenwashing</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>moderate_threshold_scale</t>
         </is>
       </c>
-      <c r="D84" s="10" t="n">
+      <c r="D84" s="6" t="n">
         <v>0.67</v>
       </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="G84" s="11" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr">
         <is>
           <t>Scaling for moderate greenwash threshold</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>greenwashing</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>moderate_penalty_scale</t>
         </is>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D85" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="G85" s="11" t="inlineStr">
         <is>
           <t>Scaling for moderate greenwash penalty</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>greenwashing</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>bu_rep_penalty</t>
         </is>
       </c>
-      <c r="D86" s="10" t="n">
+      <c r="D86" s="6" t="n">
         <v>-15</v>
       </c>
-      <c r="E86" s="8" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F86" s="8" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G86" s="11" t="inlineStr">
+      <c r="G86" s="7" t="inlineStr">
         <is>
           <t>Per-BU reputation delta on greenwashing</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>sbti_pathway</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>baseline_ci</t>
         </is>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D87" s="10" t="n">
         <v>36.25</v>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t>tCO₂e/$M</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G87" s="11" t="inlineStr">
         <is>
           <t>SBTi 1.5°C baseline carbon intensity target</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>sbti_pathway</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>annual_reduction_rate</t>
         </is>
       </c>
-      <c r="D88" s="10" t="n">
+      <c r="D88" s="6" t="n">
         <v>0.0822</v>
       </c>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
         <is>
           <t>%/yr</t>
         </is>
       </c>
-      <c r="G88" s="11" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr">
         <is>
           <t>SBTi required annual CI reduction rate (8.22%)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>sbti_pathway</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>misalignment_rounds</t>
         </is>
       </c>
-      <c r="D89" s="6" t="n">
+      <c r="D89" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>rounds</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr">
+      <c r="G89" s="11" t="inlineStr">
         <is>
           <t>Consecutive misaligned rounds before CoC surcharge</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>sbti_pathway</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>coc_surcharge</t>
         </is>
       </c>
-      <c r="D90" s="10" t="n">
+      <c r="D90" s="6" t="n">
         <v>0.005</v>
       </c>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F90" s="8" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G90" s="11" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr">
         <is>
           <t>Cost of capital surcharge for SBTi misalignment</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>sbti_pathway</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="9" t="inlineStr">
         <is>
           <t>credibility_per_round</t>
         </is>
       </c>
-      <c r="D91" s="6" t="n">
+      <c r="D91" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr">
+      <c r="G91" s="11" t="inlineStr">
         <is>
           <t>Credibility score increment per aligned round</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>eu_taxonomy</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>ci_threshold</t>
         </is>
       </c>
-      <c r="D92" s="10" t="n">
+      <c r="D92" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E92" s="8" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F92" s="8" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>tCO₂e/$M</t>
         </is>
       </c>
-      <c r="G92" s="11" t="inlineStr">
+      <c r="G92" s="7" t="inlineStr">
         <is>
           <t>CI below this → BU revenue counts as taxonomy-aligned</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>eu_taxonomy</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>green_threshold_pct</t>
         </is>
       </c>
-      <c r="D93" s="6" t="n">
+      <c r="D93" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="F93" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr">
+      <c r="G93" s="11" t="inlineStr">
         <is>
           <t>Taxonomy alignment % above this → green finance discount</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>eu_taxonomy</t>
         </is>
       </c>
-      <c r="C94" s="9" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>brown_threshold_pct</t>
         </is>
       </c>
-      <c r="D94" s="10" t="n">
+      <c r="D94" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="E94" s="8" t="inlineStr">
+      <c r="E94" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F94" s="8" t="inlineStr">
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G94" s="11" t="inlineStr">
+      <c r="G94" s="7" t="inlineStr">
         <is>
           <t>Taxonomy alignment % below this → brown penalty</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>eu_taxonomy</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="9" t="inlineStr">
         <is>
           <t>coc_benefit</t>
         </is>
       </c>
-      <c r="D95" s="6" t="n">
+      <c r="D95" s="10" t="n">
         <v>-0.005</v>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr">
+      <c r="G95" s="11" t="inlineStr">
         <is>
           <t>CoC benefit for exceeding green threshold (negative)</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>eu_taxonomy</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>coc_surcharge</t>
         </is>
       </c>
-      <c r="D96" s="10" t="n">
+      <c r="D96" s="6" t="n">
         <v>0.005</v>
       </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G96" s="11" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr">
         <is>
           <t>CoC surcharge for falling below brown threshold</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>cbam</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>ci_threshold</t>
         </is>
       </c>
-      <c r="D97" s="6" t="n">
+      <c r="D97" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E97" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="F97" s="8" t="inlineStr">
         <is>
           <t>tCO₂e/$M</t>
         </is>
       </c>
-      <c r="G97" s="7" t="inlineStr">
+      <c r="G97" s="11" t="inlineStr">
         <is>
           <t>Average CI above this triggers CBAM border adjustment</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>cbam</t>
         </is>
       </c>
-      <c r="C98" s="9" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>scope12_fraction</t>
         </is>
       </c>
-      <c r="D98" s="10" t="n">
+      <c r="D98" s="6" t="n">
         <v>0.35</v>
       </c>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F98" s="8" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="G98" s="11" t="inlineStr">
+      <c r="G98" s="7" t="inlineStr">
         <is>
           <t>Scope 1+2 ratio fraction for CBAM eligibility</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>cbam</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>surcharge_rate</t>
         </is>
       </c>
-      <c r="D99" s="6" t="n">
+      <c r="D99" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="E99" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F99" s="8" t="inlineStr">
         <is>
           <t>$/tCO₂e</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr">
+      <c r="G99" s="11" t="inlineStr">
         <is>
           <t>CBAM surcharge rate per tonne CO₂e</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>regulatory_ratchet</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="D100" s="10" t="n">
+      <c r="D100" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F100" s="8" t="inlineStr">
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G100" s="11" t="inlineStr">
+      <c r="G100" s="7" t="inlineStr">
         <is>
           <t>Starting governance risk baseline for regulatory fines</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>regulatory_ratchet</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" s="9" t="inlineStr">
         <is>
           <t>round_increment</t>
         </is>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D101" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
         <is>
           <t>pts/2rnd</t>
         </is>
       </c>
-      <c r="G101" s="7" t="inlineStr">
+      <c r="G101" s="11" t="inlineStr">
         <is>
           <t>Baseline increment per 2 rounds (ratchet tightening)</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>regulatory_ratchet</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>fine_per_point</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n">
+      <c r="D102" s="6" t="n">
         <v>500000</v>
       </c>
-      <c r="E102" s="8" t="inlineStr">
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F102" s="8" t="inlineStr">
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>$/pt</t>
         </is>
       </c>
-      <c r="G102" s="11" t="inlineStr">
+      <c r="G102" s="7" t="inlineStr">
         <is>
           <t>Regulatory fine per governance risk point over baseline</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>supplier_defection</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C103" s="9" t="inlineStr">
         <is>
           <t>inv_threshold</t>
         </is>
       </c>
-      <c r="D103" s="6" t="n">
+      <c r="D103" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr">
+      <c r="G103" s="11" t="inlineStr">
         <is>
           <t>Investment ratio below this + strict ESG → defection</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>supplier_defection</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>opex_multiplier</t>
         </is>
       </c>
-      <c r="D104" s="10" t="n">
+      <c r="D104" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="E104" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F104" s="8" t="inlineStr">
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G104" s="11" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr">
         <is>
           <t>OPEX shock multiplier on supplier defection (+10%)</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>supplier_defection</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C105" s="9" t="inlineStr">
         <is>
           <t>rev_multiplier</t>
         </is>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D105" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr">
+      <c r="G105" s="11" t="inlineStr">
         <is>
           <t>Revenue shock multiplier on supplier defection (-5%)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>cfo_austerity</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>loan_ratio_trigger</t>
         </is>
       </c>
-      <c r="D106" s="10" t="n">
+      <c r="D106" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E106" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F106" s="8" t="inlineStr">
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="G106" s="11" t="inlineStr">
+      <c r="G106" s="7" t="inlineStr">
         <is>
           <t>Loan-to-treasury ratio that triggers CFO austerity freeze</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>cash_conversion</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C107" s="9" t="inlineStr">
         <is>
           <t>gov_risk_divisor</t>
         </is>
       </c>
-      <c r="D107" s="6" t="n">
+      <c r="D107" s="10" t="n">
         <v>500</v>
       </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
         <is>
           <t>divisor</t>
         </is>
       </c>
-      <c r="G107" s="7" t="inlineStr">
+      <c r="G107" s="11" t="inlineStr">
         <is>
           <t>Governance risk divisor in cash conversion efficiency</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>cash_conversion</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>efficiency_floor</t>
         </is>
       </c>
-      <c r="D108" s="10" t="n">
+      <c r="D108" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F108" s="8" t="inlineStr">
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="G108" s="11" t="inlineStr">
+      <c r="G108" s="7" t="inlineStr">
         <is>
           <t>Minimum cash conversion efficiency floor</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>dso</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>baseline_factor</t>
         </is>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D109" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G109" s="7" t="inlineStr">
+      <c r="G109" s="11" t="inlineStr">
         <is>
           <t>DSO baseline deferred revenue factor</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>dso</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>gov_risk_scaling</t>
         </is>
       </c>
-      <c r="D110" s="10" t="n">
+      <c r="D110" s="6" t="n">
         <v>0.001</v>
       </c>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F110" s="8" t="inlineStr">
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
       </c>
-      <c r="G110" s="11" t="inlineStr">
+      <c r="G110" s="7" t="inlineStr">
         <is>
           <t>DSO scaling per unit of governance risk</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>dso</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C111" s="9" t="inlineStr">
         <is>
           <t>max_cap</t>
         </is>
       </c>
-      <c r="D111" s="6" t="n">
+      <c r="D111" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G111" s="7" t="inlineStr">
+      <c r="G111" s="11" t="inlineStr">
         <is>
           <t>Maximum DSO cap as fraction of revenue</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>macro_noise</t>
         </is>
       </c>
-      <c r="C112" s="9" t="inlineStr">
+      <c r="C112" s="5" t="inlineStr">
         <is>
           <t>inflation_band</t>
         </is>
       </c>
-      <c r="D112" s="10" t="n">
+      <c r="D112" s="6" t="n">
         <v>0.004</v>
       </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F112" s="8" t="inlineStr">
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
         <is>
           <t>±%</t>
         </is>
       </c>
-      <c r="G112" s="11" t="inlineStr">
+      <c r="G112" s="7" t="inlineStr">
         <is>
           <t>Inflation noise band per round (symmetric)</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>macro_noise</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C113" s="9" t="inlineStr">
         <is>
           <t>carbon_price_band</t>
         </is>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D113" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
         <is>
           <t>±%</t>
         </is>
       </c>
-      <c r="G113" s="7" t="inlineStr">
+      <c r="G113" s="11" t="inlineStr">
         <is>
           <t>Carbon price noise band per round (symmetric)</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>macro_noise</t>
         </is>
       </c>
-      <c r="C114" s="9" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
         <is>
           <t>micro_strike_probability</t>
         </is>
       </c>
-      <c r="D114" s="10" t="n">
+      <c r="D114" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
         <is>
           <t>prob</t>
         </is>
       </c>
-      <c r="G114" s="11" t="inlineStr">
+      <c r="G114" s="7" t="inlineStr">
         <is>
           <t>Per-round probability of a micro-strike event</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>macro_noise</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
+      <c r="C115" s="9" t="inlineStr">
         <is>
           <t>micro_strike_opex_rate</t>
         </is>
       </c>
-      <c r="D115" s="6" t="n">
+      <c r="D115" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G115" s="7" t="inlineStr">
+      <c r="G115" s="11" t="inlineStr">
         <is>
           <t>OPEX penalty rate when micro-strike fires</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>fx_risk</t>
         </is>
       </c>
-      <c r="C116" s="9" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
         <is>
           <t>movement_band</t>
         </is>
       </c>
-      <c r="D116" s="10" t="n">
+      <c r="D116" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F116" s="8" t="inlineStr">
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
         <is>
           <t>±%</t>
         </is>
       </c>
-      <c r="G116" s="11" t="inlineStr">
+      <c r="G116" s="7" t="inlineStr">
         <is>
           <t>FX movement band per round (symmetric ±7%)</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>fx_risk</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C117" s="9" t="inlineStr">
         <is>
           <t>default_exposure</t>
         </is>
       </c>
-      <c r="D117" s="6" t="n">
+      <c r="D117" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G117" s="7" t="inlineStr">
+      <c r="G117" s="11" t="inlineStr">
         <is>
           <t>Default foreign revenue exposure for unlisted BUs</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>emissions_breach</t>
         </is>
       </c>
-      <c r="C118" s="9" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>rep_penalty</t>
         </is>
       </c>
-      <c r="D118" s="10" t="n">
+      <c r="D118" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="inlineStr">
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G118" s="11" t="inlineStr">
+      <c r="G118" s="7" t="inlineStr">
         <is>
           <t>Reputation penalty for carbon emissions breach</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>stranded_assets</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C119" s="9" t="inlineStr">
         <is>
           <t>ci_threshold</t>
         </is>
       </c>
-      <c r="D119" s="6" t="n">
+      <c r="D119" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="E119" s="4" t="inlineStr">
+      <c r="E119" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr">
+      <c r="F119" s="8" t="inlineStr">
         <is>
           <t>tCO₂e/$M</t>
         </is>
       </c>
-      <c r="G119" s="7" t="inlineStr">
+      <c r="G119" s="11" t="inlineStr">
         <is>
           <t>CI above this → BU classified as stranded asset</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>stranded_assets</t>
         </is>
       </c>
-      <c r="C120" s="9" t="inlineStr">
+      <c r="C120" s="5" t="inlineStr">
         <is>
           <t>coc_surcharge</t>
         </is>
       </c>
-      <c r="D120" s="10" t="n">
+      <c r="D120" s="6" t="n">
         <v>0.015</v>
       </c>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F120" s="8" t="inlineStr">
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G120" s="11" t="inlineStr">
+      <c r="G120" s="7" t="inlineStr">
         <is>
           <t>CoC surcharge for holding stranded assets (+1.5%)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>tipping_hostility</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
+      <c r="C121" s="9" t="inlineStr">
         <is>
           <t>tipped_multiplier</t>
         </is>
       </c>
-      <c r="D121" s="6" t="n">
+      <c r="D121" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G121" s="7" t="inlineStr">
+      <c r="G121" s="11" t="inlineStr">
         <is>
           <t>NCD hostility multiplier when tipping tier = 'tipped'</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B122" s="8" t="inlineStr">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>tipping_hostility</t>
         </is>
       </c>
-      <c r="C122" s="9" t="inlineStr">
+      <c r="C122" s="5" t="inlineStr">
         <is>
           <t>stressed_multiplier</t>
         </is>
       </c>
-      <c r="D122" s="10" t="n">
+      <c r="D122" s="6" t="n">
         <v>1.75</v>
       </c>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F122" s="8" t="inlineStr">
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G122" s="11" t="inlineStr">
+      <c r="G122" s="7" t="inlineStr">
         <is>
           <t>NCD hostility multiplier when tipping tier = 'stressed'</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
         <is>
           <t>tipping_hostility</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
+      <c r="C123" s="9" t="inlineStr">
         <is>
           <t>warning_multiplier</t>
         </is>
       </c>
-      <c r="D123" s="6" t="n">
+      <c r="D123" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G123" s="7" t="inlineStr">
+      <c r="G123" s="11" t="inlineStr">
         <is>
           <t>NCD hostility multiplier when tipping tier = 'warning'</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B124" s="8" t="inlineStr">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>ncd_forgiveness</t>
         </is>
       </c>
-      <c r="C124" s="9" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
         <is>
           <t>log_coefficient</t>
         </is>
       </c>
-      <c r="D124" s="10" t="n">
+      <c r="D124" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E124" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F124" s="8" t="inlineStr">
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
         <is>
           <t>coeff</t>
         </is>
       </c>
-      <c r="G124" s="11" t="inlineStr">
+      <c r="G124" s="7" t="inlineStr">
         <is>
           <t>NCD forgiveness logarithmic scaling coefficient</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>implementation_lag</t>
         </is>
       </c>
-      <c r="C125" s="5" t="inlineStr">
+      <c r="C125" s="9" t="inlineStr">
         <is>
           <t>inv_threshold</t>
         </is>
       </c>
-      <c r="D125" s="6" t="n">
+      <c r="D125" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G125" s="7" t="inlineStr">
+      <c r="G125" s="11" t="inlineStr">
         <is>
           <t>Investment ratio threshold for synergy implementation lag</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B126" s="8" t="inlineStr">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>employer_brand</t>
         </is>
       </c>
-      <c r="C126" s="9" t="inlineStr">
+      <c r="C126" s="5" t="inlineStr">
         <is>
           <t>penalty_threshold</t>
         </is>
       </c>
-      <c r="D126" s="10" t="n">
+      <c r="D126" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="E126" s="8" t="inlineStr">
+      <c r="E126" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F126" s="8" t="inlineStr">
+      <c r="F126" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G126" s="11" t="inlineStr">
+      <c r="G126" s="7" t="inlineStr">
         <is>
           <t>Employer brand score below this → OPEX penalty</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
         <is>
           <t>employer_brand</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr">
+      <c r="C127" s="9" t="inlineStr">
         <is>
           <t>max_penalty_rate</t>
         </is>
       </c>
-      <c r="D127" s="6" t="n">
+      <c r="D127" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F127" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G127" s="7" t="inlineStr">
+      <c r="G127" s="11" t="inlineStr">
         <is>
           <t>Max employer brand OPEX penalty rate</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B128" s="8" t="inlineStr">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>patient_outcomes</t>
         </is>
       </c>
-      <c r="C128" s="9" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="D128" s="10" t="n">
+      <c r="D128" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="E128" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F128" s="8" t="inlineStr">
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G128" s="11" t="inlineStr">
+      <c r="G128" s="7" t="inlineStr">
         <is>
           <t>Patient outcomes score baseline for revenue modifier</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>patient_outcomes</t>
         </is>
       </c>
-      <c r="C129" s="5" t="inlineStr">
+      <c r="C129" s="9" t="inlineStr">
         <is>
           <t>divisor</t>
         </is>
       </c>
-      <c r="D129" s="6" t="n">
+      <c r="D129" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F129" s="8" t="inlineStr">
         <is>
           <t>divisor</t>
         </is>
       </c>
-      <c r="G129" s="7" t="inlineStr">
+      <c r="G129" s="11" t="inlineStr">
         <is>
           <t>Patient outcomes divisor in revenue modifier formula</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B130" s="8" t="inlineStr">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>patient_outcomes</t>
         </is>
       </c>
-      <c r="C130" s="9" t="inlineStr">
+      <c r="C130" s="5" t="inlineStr">
         <is>
           <t>modifier_min</t>
         </is>
       </c>
-      <c r="D130" s="10" t="n">
+      <c r="D130" s="6" t="n">
         <v>0.75</v>
       </c>
-      <c r="E130" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F130" s="8" t="inlineStr">
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G130" s="11" t="inlineStr">
+      <c r="G130" s="7" t="inlineStr">
         <is>
           <t>Minimum patient outcomes revenue modifier</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>patient_outcomes</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
+      <c r="C131" s="9" t="inlineStr">
         <is>
           <t>modifier_max</t>
         </is>
       </c>
-      <c r="D131" s="6" t="n">
+      <c r="D131" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F131" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G131" s="7" t="inlineStr">
+      <c r="G131" s="11" t="inlineStr">
         <is>
           <t>Maximum patient outcomes revenue modifier</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="inlineStr">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>utilization</t>
         </is>
       </c>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
         <is>
           <t>overload_threshold</t>
         </is>
       </c>
-      <c r="D132" s="10" t="n">
+      <c r="D132" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="E132" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F132" s="8" t="inlineStr">
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G132" s="11" t="inlineStr">
+      <c r="G132" s="7" t="inlineStr">
         <is>
           <t>Bed utilization above this → burnout increment</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>utilization</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
+      <c r="C133" s="9" t="inlineStr">
         <is>
           <t>overload_burnout_increment</t>
         </is>
       </c>
-      <c r="D133" s="6" t="n">
+      <c r="D133" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F133" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G133" s="7" t="inlineStr">
+      <c r="G133" s="11" t="inlineStr">
         <is>
           <t>Burnout increment per round when utilization overloaded</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B134" s="8" t="inlineStr">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>utilization</t>
         </is>
       </c>
-      <c r="C134" s="9" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
         <is>
           <t>drift_rate</t>
         </is>
       </c>
-      <c r="D134" s="10" t="n">
+      <c r="D134" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="E134" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F134" s="8" t="inlineStr">
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
         <is>
           <t>%/round</t>
         </is>
       </c>
-      <c r="G134" s="11" t="inlineStr">
+      <c r="G134" s="7" t="inlineStr">
         <is>
           <t>Bed utilization natural drift rate toward 100%</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>imitation_decay</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
+      <c r="C135" s="9" t="inlineStr">
         <is>
           <t>default_rate</t>
         </is>
       </c>
-      <c r="D135" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
+      <c r="D135" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E135" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F135" s="8" t="inlineStr">
         <is>
           <t>%/round</t>
         </is>
       </c>
-      <c r="G135" s="7" t="inlineStr">
+      <c r="G135" s="11" t="inlineStr">
         <is>
           <t>Default VRIO imitation decay rate per round</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C136" s="9" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>severity_routine_ceiling</t>
         </is>
       </c>
-      <c r="D136" s="10" t="n">
+      <c r="D136" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E136" s="8" t="inlineStr">
+      <c r="E136" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F136" s="8" t="inlineStr">
+      <c r="F136" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G136" s="11" t="inlineStr">
+      <c r="G136" s="7" t="inlineStr">
         <is>
           <t>Treasury impact below this → classified as 'routine'</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C137" s="5" t="inlineStr">
+      <c r="C137" s="9" t="inlineStr">
         <is>
           <t>severity_noteworthy_ceiling</t>
         </is>
       </c>
-      <c r="D137" s="6" t="n">
+      <c r="D137" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="E137" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F137" s="4" t="inlineStr">
+      <c r="F137" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G137" s="7" t="inlineStr">
+      <c r="G137" s="11" t="inlineStr">
         <is>
           <t>Treasury impact below this → 'noteworthy'</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C138" s="9" t="inlineStr">
+      <c r="C138" s="5" t="inlineStr">
         <is>
           <t>severity_material_ceiling</t>
         </is>
       </c>
-      <c r="D138" s="10" t="n">
+      <c r="D138" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="E138" s="8" t="inlineStr">
+      <c r="E138" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F138" s="8" t="inlineStr">
+      <c r="F138" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G138" s="11" t="inlineStr">
+      <c r="G138" s="7" t="inlineStr">
         <is>
           <t>Treasury impact below this → 'material'</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="C139" s="9" t="inlineStr">
         <is>
           <t>sdg_grade_a_plus</t>
         </is>
       </c>
-      <c r="D139" s="6" t="n">
+      <c r="D139" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="E139" s="4" t="inlineStr">
+      <c r="E139" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F139" s="4" t="inlineStr">
+      <c r="F139" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G139" s="7" t="inlineStr">
+      <c r="G139" s="11" t="inlineStr">
         <is>
           <t>SDG weighted score ≥ this → grade A+</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C140" s="9" t="inlineStr">
+      <c r="C140" s="5" t="inlineStr">
         <is>
           <t>sdg_grade_a</t>
         </is>
       </c>
-      <c r="D140" s="10" t="n">
+      <c r="D140" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="E140" s="8" t="inlineStr">
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F140" s="8" t="inlineStr">
+      <c r="F140" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G140" s="11" t="inlineStr">
+      <c r="G140" s="7" t="inlineStr">
         <is>
           <t>SDG weighted score ≥ this → grade A</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
+      <c r="C141" s="9" t="inlineStr">
         <is>
           <t>sdg_grade_b</t>
         </is>
       </c>
-      <c r="D141" s="6" t="n">
+      <c r="D141" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="E141" s="4" t="inlineStr">
+      <c r="E141" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F141" s="4" t="inlineStr">
+      <c r="F141" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G141" s="7" t="inlineStr">
+      <c r="G141" s="11" t="inlineStr">
         <is>
           <t>SDG weighted score ≥ this → grade B</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C142" s="9" t="inlineStr">
+      <c r="C142" s="5" t="inlineStr">
         <is>
           <t>sdg_grade_c</t>
         </is>
       </c>
-      <c r="D142" s="10" t="n">
+      <c r="D142" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="E142" s="8" t="inlineStr">
+      <c r="E142" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F142" s="8" t="inlineStr">
+      <c r="F142" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G142" s="11" t="inlineStr">
+      <c r="G142" s="7" t="inlineStr">
         <is>
           <t>SDG weighted score ≥ this → grade C</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
+      <c r="C143" s="9" t="inlineStr">
         <is>
           <t>sdg_grade_d</t>
         </is>
       </c>
-      <c r="D143" s="6" t="n">
+      <c r="D143" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="E143" s="4" t="inlineStr">
+      <c r="E143" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F143" s="4" t="inlineStr">
+      <c r="F143" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G143" s="7" t="inlineStr">
+      <c r="G143" s="11" t="inlineStr">
         <is>
           <t>SDG weighted score ≥ this → grade D</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C144" s="9" t="inlineStr">
+      <c r="C144" s="5" t="inlineStr">
         <is>
           <t>caroic_grade_a_plus</t>
         </is>
       </c>
-      <c r="D144" s="10" t="n">
+      <c r="D144" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E144" s="8" t="inlineStr">
+      <c r="E144" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F144" s="8" t="inlineStr">
+      <c r="F144" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G144" s="11" t="inlineStr">
+      <c r="G144" s="7" t="inlineStr">
         <is>
           <t>CAROIC ≥ this → grade A+</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr">
+      <c r="C145" s="9" t="inlineStr">
         <is>
           <t>caroic_grade_a</t>
         </is>
       </c>
-      <c r="D145" s="6" t="n">
+      <c r="D145" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="E145" s="4" t="inlineStr">
+      <c r="E145" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr">
+      <c r="F145" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G145" s="7" t="inlineStr">
+      <c r="G145" s="11" t="inlineStr">
         <is>
           <t>CAROIC ≥ this → grade A</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C146" s="9" t="inlineStr">
+      <c r="C146" s="5" t="inlineStr">
         <is>
           <t>caroic_grade_b</t>
         </is>
       </c>
-      <c r="D146" s="10" t="n">
+      <c r="D146" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E146" s="8" t="inlineStr">
+      <c r="E146" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F146" s="8" t="inlineStr">
+      <c r="F146" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G146" s="11" t="inlineStr">
+      <c r="G146" s="7" t="inlineStr">
         <is>
           <t>CAROIC ≥ this → grade B</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C147" s="5" t="inlineStr">
+      <c r="C147" s="9" t="inlineStr">
         <is>
           <t>caroic_grade_c</t>
         </is>
       </c>
-      <c r="D147" s="6" t="n">
+      <c r="D147" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E147" s="4" t="inlineStr">
+      <c r="E147" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr">
+      <c r="F147" s="8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G147" s="7" t="inlineStr">
+      <c r="G147" s="11" t="inlineStr">
         <is>
           <t>CAROIC ≥ this → grade C</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C148" s="9" t="inlineStr">
+      <c r="C148" s="5" t="inlineStr">
         <is>
           <t>cri_weight_gov_risk</t>
         </is>
       </c>
-      <c r="D148" s="10" t="n">
+      <c r="D148" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="E148" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F148" s="8" t="inlineStr">
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="G148" s="11" t="inlineStr">
+      <c r="G148" s="7" t="inlineStr">
         <is>
           <t>Governance risk weight in Contagion Risk Index</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
+      <c r="C149" s="9" t="inlineStr">
         <is>
           <t>cri_weight_slo_deficit</t>
         </is>
       </c>
-      <c r="D149" s="6" t="n">
+      <c r="D149" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
+      <c r="E149" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F149" s="8" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="G149" s="7" t="inlineStr">
+      <c r="G149" s="11" t="inlineStr">
         <is>
           <t>SLO deficit weight in Contagion Risk Index</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C150" s="9" t="inlineStr">
+      <c r="C150" s="5" t="inlineStr">
         <is>
           <t>cri_weight_rep_deficit</t>
         </is>
       </c>
-      <c r="D150" s="10" t="n">
+      <c r="D150" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="E150" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F150" s="8" t="inlineStr">
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="G150" s="11" t="inlineStr">
+      <c r="G150" s="7" t="inlineStr">
         <is>
           <t>Reputation deficit weight in Contagion Risk Index</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
+      <c r="A151" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C151" s="5" t="inlineStr">
+      <c r="C151" s="9" t="inlineStr">
         <is>
           <t>cri_weight_carbon</t>
         </is>
       </c>
-      <c r="D151" s="6" t="n">
+      <c r="D151" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F151" s="8" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="G151" s="7" t="inlineStr">
+      <c r="G151" s="11" t="inlineStr">
         <is>
           <t>Carbon intensity weight in Contagion Risk Index</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B152" s="8" t="inlineStr">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C152" s="9" t="inlineStr">
+      <c r="C152" s="5" t="inlineStr">
         <is>
           <t>cri_tier_low</t>
         </is>
       </c>
-      <c r="D152" s="10" t="n">
+      <c r="D152" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E152" s="8" t="inlineStr">
+      <c r="E152" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F152" s="8" t="inlineStr">
+      <c r="F152" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G152" s="11" t="inlineStr">
+      <c r="G152" s="7" t="inlineStr">
         <is>
           <t>CRI below this → 'Low' risk label</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C153" s="5" t="inlineStr">
+      <c r="C153" s="9" t="inlineStr">
         <is>
           <t>cri_tier_moderate</t>
         </is>
       </c>
-      <c r="D153" s="6" t="n">
+      <c r="D153" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="E153" s="4" t="inlineStr">
+      <c r="E153" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F153" s="4" t="inlineStr">
+      <c r="F153" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G153" s="7" t="inlineStr">
+      <c r="G153" s="11" t="inlineStr">
         <is>
           <t>CRI below this → 'Moderate' risk label</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C154" s="9" t="inlineStr">
+      <c r="C154" s="5" t="inlineStr">
         <is>
           <t>cri_tier_high</t>
         </is>
       </c>
-      <c r="D154" s="10" t="n">
+      <c r="D154" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="E154" s="8" t="inlineStr">
+      <c r="E154" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F154" s="8" t="inlineStr">
+      <c r="F154" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G154" s="11" t="inlineStr">
+      <c r="G154" s="7" t="inlineStr">
         <is>
           <t>CRI below this → 'High' risk label</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
+      <c r="C155" s="9" t="inlineStr">
         <is>
           <t>momentum_weight_treasury</t>
         </is>
       </c>
-      <c r="D155" s="6" t="n">
+      <c r="D155" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
+      <c r="E155" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F155" s="8" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="G155" s="7" t="inlineStr">
+      <c r="G155" s="11" t="inlineStr">
         <is>
           <t>Treasury velocity weight in momentum score</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C156" s="9" t="inlineStr">
+      <c r="C156" s="5" t="inlineStr">
         <is>
           <t>momentum_weight_rep</t>
         </is>
       </c>
-      <c r="D156" s="10" t="n">
+      <c r="D156" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="E156" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F156" s="8" t="inlineStr">
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="G156" s="11" t="inlineStr">
+      <c r="G156" s="7" t="inlineStr">
         <is>
           <t>Reputation delta weight in momentum score</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C157" s="5" t="inlineStr">
+      <c r="C157" s="9" t="inlineStr">
         <is>
           <t>momentum_weight_ncd</t>
         </is>
       </c>
-      <c r="D157" s="6" t="n">
+      <c r="D157" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F157" s="8" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="G157" s="7" t="inlineStr">
+      <c r="G157" s="11" t="inlineStr">
         <is>
           <t>NCD delta weight in momentum score</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B158" s="8" t="inlineStr">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C158" s="9" t="inlineStr">
+      <c r="C158" s="5" t="inlineStr">
         <is>
           <t>momentum_high_threshold</t>
         </is>
       </c>
-      <c r="D158" s="10" t="n">
+      <c r="D158" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="E158" s="8" t="inlineStr">
+      <c r="E158" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F158" s="8" t="inlineStr">
+      <c r="F158" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G158" s="11" t="inlineStr">
+      <c r="G158" s="7" t="inlineStr">
         <is>
           <t>Momentum score above this → 'High Momentum' label</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C159" s="5" t="inlineStr">
+      <c r="C159" s="9" t="inlineStr">
         <is>
           <t>momentum_comeback_mr_bonus</t>
         </is>
       </c>
-      <c r="D159" s="6" t="n">
+      <c r="D159" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F159" s="4" t="inlineStr">
+      <c r="E159" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F159" s="8" t="inlineStr">
         <is>
           <t>bonus</t>
         </is>
       </c>
-      <c r="G159" s="7" t="inlineStr">
+      <c r="G159" s="11" t="inlineStr">
         <is>
           <t>Market-relative bonus for 'Comeback Kid' momentum</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C160" s="9" t="inlineStr">
+      <c r="C160" s="5" t="inlineStr">
         <is>
           <t>momentum_treasury_norm</t>
         </is>
       </c>
-      <c r="D160" s="10" t="n">
+      <c r="D160" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="E160" s="8" t="inlineStr">
+      <c r="E160" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F160" s="8" t="inlineStr">
+      <c r="F160" s="4" t="inlineStr">
         <is>
           <t>divisor</t>
         </is>
       </c>
-      <c r="G160" s="11" t="inlineStr">
+      <c r="G160" s="7" t="inlineStr">
         <is>
           <t>Treasury velocity normalization factor</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C161" s="5" t="inlineStr">
+      <c r="C161" s="9" t="inlineStr">
         <is>
           <t>momentum_rep_multiplier</t>
         </is>
       </c>
-      <c r="D161" s="6" t="n">
+      <c r="D161" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E161" s="4" t="inlineStr">
+      <c r="E161" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F161" s="4" t="inlineStr">
+      <c r="F161" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G161" s="7" t="inlineStr">
+      <c r="G161" s="11" t="inlineStr">
         <is>
           <t>Reputation delta multiplier in momentum score</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C162" s="9" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
         <is>
           <t>momentum_ncd_multiplier</t>
         </is>
       </c>
-      <c r="D162" s="10" t="n">
+      <c r="D162" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E162" s="8" t="inlineStr">
+      <c r="E162" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F162" s="8" t="inlineStr">
+      <c r="F162" s="4" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G162" s="11" t="inlineStr">
+      <c r="G162" s="7" t="inlineStr">
         <is>
           <t>NCD delta multiplier in momentum score</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="A163" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B163" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C163" s="5" t="inlineStr">
+      <c r="C163" s="9" t="inlineStr">
         <is>
           <t>insolvency_warning_rounds</t>
         </is>
       </c>
-      <c r="D163" s="6" t="n">
+      <c r="D163" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E163" s="4" t="inlineStr">
+      <c r="E163" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F163" s="4" t="inlineStr">
+      <c r="F163" s="8" t="inlineStr">
         <is>
           <t>rounds</t>
         </is>
       </c>
-      <c r="G163" s="7" t="inlineStr">
+      <c r="G163" s="11" t="inlineStr">
         <is>
           <t>Rounds of negative treasury before insolvency warning</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C164" s="9" t="inlineStr">
+      <c r="C164" s="5" t="inlineStr">
         <is>
           <t>time_to_impact_horizon</t>
         </is>
       </c>
-      <c r="D164" s="10" t="n">
+      <c r="D164" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E164" s="8" t="inlineStr">
+      <c r="E164" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F164" s="8" t="inlineStr">
+      <c r="F164" s="4" t="inlineStr">
         <is>
           <t>rounds</t>
         </is>
       </c>
-      <c r="G164" s="11" t="inlineStr">
+      <c r="G164" s="7" t="inlineStr">
         <is>
           <t>Forecast look-ahead horizon for time-to-impact</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B165" s="4" t="inlineStr">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C165" s="5" t="inlineStr">
+      <c r="C165" s="9" t="inlineStr">
         <is>
           <t>braindrain_rep_threshold</t>
         </is>
       </c>
-      <c r="D165" s="6" t="n">
+      <c r="D165" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="E165" s="4" t="inlineStr">
+      <c r="E165" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F165" s="4" t="inlineStr">
+      <c r="F165" s="8" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G165" s="7" t="inlineStr">
+      <c r="G165" s="11" t="inlineStr">
         <is>
           <t>Reputation below this → brain-drain warning in forecast</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C166" s="9" t="inlineStr">
+      <c r="C166" s="5" t="inlineStr">
         <is>
           <t>strike_warning_threshold</t>
         </is>
       </c>
-      <c r="D166" s="10" t="n">
+      <c r="D166" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="E166" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F166" s="8" t="inlineStr">
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
         <is>
           <t>prob</t>
         </is>
       </c>
-      <c r="G166" s="11" t="inlineStr">
+      <c r="G166" s="7" t="inlineStr">
         <is>
           <t>Strike probability above this → warning</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
+      <c r="A167" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C167" s="5" t="inlineStr">
+      <c r="C167" s="9" t="inlineStr">
         <is>
           <t>strike_critical_threshold</t>
         </is>
       </c>
-      <c r="D167" s="6" t="n">
+      <c r="D167" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr">
+      <c r="E167" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F167" s="8" t="inlineStr">
         <is>
           <t>prob</t>
         </is>
       </c>
-      <c r="G167" s="7" t="inlineStr">
+      <c r="G167" s="11" t="inlineStr">
         <is>
           <t>Strike probability above this → critical</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="8" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
         <is>
           <t>scoring</t>
         </is>
       </c>
-      <c r="C168" s="9" t="inlineStr">
+      <c r="C168" s="5" t="inlineStr">
         <is>
           <t>contagion_risk_warning_threshold</t>
         </is>
       </c>
-      <c r="D168" s="10" t="n">
+      <c r="D168" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E168" s="8" t="inlineStr">
+      <c r="E168" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F168" s="8" t="inlineStr">
+      <c r="F168" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G168" s="11" t="inlineStr">
+      <c r="G168" s="7" t="inlineStr">
         <is>
           <t>CRI above this → board reflection trigger</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t>Engine Parameters</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="n"/>
-      <c r="C169" s="3" t="n"/>
-      <c r="D169" s="3" t="n"/>
-      <c r="E169" s="3" t="n"/>
-      <c r="F169" s="3" t="n"/>
-      <c r="G169" s="3" t="n"/>
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>treasury_drop_reflection_pct</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F169" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G169" s="11" t="inlineStr">
+        <is>
+          <t>Treasury drop above this % → board reflection trigger</t>
+        </is>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="36" t="inlineStr">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>slo_ramp</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>no_decay_ratio</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>Investment ratio at/above which SLO stops decaying (default 0.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>slo_ramp</t>
+        </is>
+      </c>
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>mid_ratio</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E171" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F171" s="8" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="G171" s="11" t="inlineStr">
+        <is>
+          <t>Investment ratio at/above which SLO grows mildly (default 0.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>slo_ramp</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>growth_ratio</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>Investment ratio at/above which SLO grows fully (default 0.50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="8" t="inlineStr">
+        <is>
+          <t>Engine Parameters</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="inlineStr">
+        <is>
+          <t>slo_ramp</t>
+        </is>
+      </c>
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>min_abs_capex</t>
+        </is>
+      </c>
+      <c r="D173" s="10" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F173" s="8" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="G173" s="11" t="inlineStr">
+        <is>
+          <t>Minimum absolute per-BU CapEx that counts as invested (default 500,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="21" t="inlineStr">
         <is>
           <t>🌪️ Climate Value-at-Risk</t>
         </is>
       </c>
-      <c r="B170" s="3" t="n"/>
-      <c r="C170" s="3" t="n"/>
-      <c r="D170" s="3" t="n"/>
-      <c r="E170" s="3" t="n"/>
-      <c r="F170" s="3" t="n"/>
-      <c r="G170" s="3" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>Climate Value-at-Risk</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr"/>
-      <c r="C171" s="5" t="inlineStr">
-        <is>
-          <t>cyclone_prob_base</t>
-        </is>
-      </c>
-      <c r="D171" s="6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>prob</t>
-        </is>
-      </c>
-      <c r="G171" s="7" t="inlineStr">
-        <is>
-          <t>Base cyclone probability for Climate VaR physical risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="8" t="inlineStr">
-        <is>
-          <t>Climate Value-at-Risk</t>
-        </is>
-      </c>
-      <c r="B172" s="8" t="inlineStr"/>
-      <c r="C172" s="9" t="inlineStr">
-        <is>
-          <t>cyclone_prob_tipped</t>
-        </is>
-      </c>
-      <c r="D172" s="10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E172" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F172" s="8" t="inlineStr">
-        <is>
-          <t>prob</t>
-        </is>
-      </c>
-      <c r="G172" s="11" t="inlineStr">
-        <is>
-          <t>Cyclone probability when tipping tier = 'tipped'</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>Climate Value-at-Risk</t>
-        </is>
-      </c>
-      <c r="B173" s="4" t="inlineStr"/>
-      <c r="C173" s="5" t="inlineStr">
-        <is>
-          <t>cyclone_prob_stressed</t>
-        </is>
-      </c>
-      <c r="D173" s="6" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>prob</t>
-        </is>
-      </c>
-      <c r="G173" s="7" t="inlineStr">
-        <is>
-          <t>Cyclone probability when tipping tier = 'stressed'</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="8" t="inlineStr">
-        <is>
-          <t>Climate Value-at-Risk</t>
-        </is>
-      </c>
-      <c r="B174" s="8" t="inlineStr"/>
-      <c r="C174" s="9" t="inlineStr">
-        <is>
-          <t>cyclone_prob_warning</t>
-        </is>
-      </c>
-      <c r="D174" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E174" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F174" s="8" t="inlineStr">
-        <is>
-          <t>prob</t>
-        </is>
-      </c>
-      <c r="G174" s="11" t="inlineStr">
-        <is>
-          <t>Cyclone probability when tipping tier = 'warning'</t>
-        </is>
-      </c>
+      <c r="B174" s="3" t="n"/>
+      <c r="C174" s="3" t="n"/>
+      <c r="D174" s="3" t="n"/>
+      <c r="E174" s="3" t="n"/>
+      <c r="F174" s="3" t="n"/>
+      <c r="G174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -6376,25 +6363,25 @@
       <c r="B175" s="4" t="inlineStr"/>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>physical_damage_base</t>
+          <t>cyclone_prob_base</t>
         </is>
       </c>
       <c r="D175" s="6" t="n">
-        <v>12000000</v>
+        <v>0.75</v>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>prob</t>
         </is>
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>Physical VaR maximum damage exposure (base)</t>
+          <t>Base cyclone probability for Climate VaR physical risk</t>
         </is>
       </c>
     </row>
@@ -6407,25 +6394,25 @@
       <c r="B176" s="8" t="inlineStr"/>
       <c r="C176" s="9" t="inlineStr">
         <is>
-          <t>tipping_ci_warning</t>
+          <t>cyclone_prob_tipped</t>
         </is>
       </c>
       <c r="D176" s="10" t="n">
-        <v>45</v>
+        <v>0.9</v>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr">
         <is>
-          <t>tCO₂e/$M</t>
+          <t>prob</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
-          <t>Avg CI above this → climate 'warning' tipping tier</t>
+          <t>Cyclone probability when tipping tier = 'tipped'</t>
         </is>
       </c>
     </row>
@@ -6438,25 +6425,25 @@
       <c r="B177" s="4" t="inlineStr"/>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>tipping_ci_stressed</t>
+          <t>cyclone_prob_stressed</t>
         </is>
       </c>
       <c r="D177" s="6" t="n">
-        <v>55</v>
+        <v>0.85</v>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>tCO₂e/$M</t>
+          <t>prob</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>Avg CI above this → climate 'stressed' tipping tier</t>
+          <t>Cyclone probability when tipping tier = 'stressed'</t>
         </is>
       </c>
     </row>
@@ -6469,25 +6456,25 @@
       <c r="B178" s="8" t="inlineStr"/>
       <c r="C178" s="9" t="inlineStr">
         <is>
-          <t>tipping_ci_tipped</t>
+          <t>cyclone_prob_warning</t>
         </is>
       </c>
       <c r="D178" s="10" t="n">
-        <v>65</v>
+        <v>0.8</v>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr">
         <is>
-          <t>tCO₂e/$M</t>
+          <t>prob</t>
         </is>
       </c>
       <c r="G178" s="11" t="inlineStr">
         <is>
-          <t>Avg CI above this → irreversible 'tipped' tier</t>
+          <t>Cyclone probability when tipping tier = 'warning'</t>
         </is>
       </c>
     </row>
@@ -6500,11 +6487,11 @@
       <c r="B179" s="4" t="inlineStr"/>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>transition_var_ci_threshold</t>
+          <t>physical_damage_base</t>
         </is>
       </c>
       <c r="D179" s="6" t="n">
-        <v>80</v>
+        <v>12000000</v>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
@@ -6513,12 +6500,12 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>tCO₂e/$M</t>
+          <t>$</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>CI above this → BU revenue counts as stranded exposure</t>
+          <t>Physical VaR maximum damage exposure (base)</t>
         </is>
       </c>
     </row>
@@ -6531,25 +6518,25 @@
       <c r="B180" s="8" t="inlineStr"/>
       <c r="C180" s="9" t="inlineStr">
         <is>
-          <t>transition_var_stranded_multiplier</t>
+          <t>tipping_ci_warning</t>
         </is>
       </c>
       <c r="D180" s="10" t="n">
-        <v>0.15</v>
+        <v>45</v>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F180" s="8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>tCO₂e/$M</t>
         </is>
       </c>
       <c r="G180" s="11" t="inlineStr">
         <is>
-          <t>Stranded exposure VaR multiplier</t>
+          <t>Avg CI above this → climate 'warning' tipping tier</t>
         </is>
       </c>
     </row>
@@ -6559,71 +6546,107 @@
           <t>Climate Value-at-Risk</t>
         </is>
       </c>
-      <c r="B181" s="3" t="n"/>
-      <c r="C181" s="3" t="n"/>
-      <c r="D181" s="3" t="n"/>
-      <c r="E181" s="3" t="n"/>
-      <c r="F181" s="3" t="n"/>
-      <c r="G181" s="3" t="n"/>
+      <c r="B181" s="4" t="inlineStr"/>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>tipping_ci_stressed</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>tCO₂e/$M</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>Avg CI above this → climate 'stressed' tipping tier</t>
+        </is>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="37" t="inlineStr">
-        <is>
-          <t>🧮 Balance Sheet Accounting</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="n"/>
-      <c r="C182" s="3" t="n"/>
-      <c r="D182" s="3" t="n"/>
-      <c r="E182" s="3" t="n"/>
-      <c r="F182" s="3" t="n"/>
-      <c r="G182" s="3" t="n"/>
+      <c r="A182" s="8" t="inlineStr">
+        <is>
+          <t>Climate Value-at-Risk</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="inlineStr"/>
+      <c r="C182" s="9" t="inlineStr">
+        <is>
+          <t>tipping_ci_tipped</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E182" s="8" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F182" s="8" t="inlineStr">
+        <is>
+          <t>tCO₂e/$M</t>
+        </is>
+      </c>
+      <c r="G182" s="11" t="inlineStr">
+        <is>
+          <t>Avg CI above this → irreversible 'tipped' tier</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Balance Sheet Accounting</t>
+          <t>Climate Value-at-Risk</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr"/>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>capex_capitalisation_rate</t>
+          <t>transition_var_ci_threshold</t>
         </is>
       </c>
       <c r="D183" s="6" t="n">
-        <v>0.6</v>
+        <v>80</v>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>tCO₂e/$M</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>Fraction of CapEx capitalised as PPE (IAS 16)</t>
+          <t>CI above this → BU revenue counts as stranded exposure</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="8" t="inlineStr">
         <is>
-          <t>Balance Sheet Accounting</t>
+          <t>Climate Value-at-Risk</t>
         </is>
       </c>
       <c r="B184" s="8" t="inlineStr"/>
       <c r="C184" s="9" t="inlineStr">
         <is>
-          <t>annual_depreciation_rate</t>
+          <t>transition_var_stranded_multiplier</t>
         </is>
       </c>
       <c r="D184" s="10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
@@ -6632,29 +6655,29 @@
       </c>
       <c r="F184" s="8" t="inlineStr">
         <is>
-          <t>%/yr</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G184" s="11" t="inlineStr">
         <is>
-          <t>Straight-line annual depreciation rate</t>
+          <t>Stranded exposure VaR multiplier</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>Balance Sheet Accounting</t>
+          <t>Climate Value-at-Risk</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr"/>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>brand_base_per_bu</t>
+          <t>transition_var_fee_years</t>
         </is>
       </c>
       <c r="D185" s="6" t="n">
-        <v>6250000</v>
+        <v>5</v>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
@@ -6663,45 +6686,27 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>years</t>
         </is>
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>Brand valuation base per business unit</t>
+          <t>Carbon fee projection horizon for transition VaR</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="8" t="inlineStr">
-        <is>
-          <t>Balance Sheet Accounting</t>
-        </is>
-      </c>
-      <c r="B186" s="8" t="inlineStr"/>
-      <c r="C186" s="9" t="inlineStr">
-        <is>
-          <t>min_environmental_provision</t>
-        </is>
-      </c>
-      <c r="D186" s="10" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="E186" s="8" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F186" s="8" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="G186" s="11" t="inlineStr">
-        <is>
-          <t>Minimum irreducible environmental provision (IAS 37)</t>
-        </is>
-      </c>
+      <c r="A186" s="22" t="inlineStr">
+        <is>
+          <t>🧮 Balance Sheet Accounting</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="n"/>
+      <c r="C186" s="3" t="n"/>
+      <c r="D186" s="3" t="n"/>
+      <c r="E186" s="3" t="n"/>
+      <c r="F186" s="3" t="n"/>
+      <c r="G186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -6709,40 +6714,76 @@
           <t>Balance Sheet Accounting</t>
         </is>
       </c>
-      <c r="B187" s="3" t="n"/>
-      <c r="C187" s="3" t="n"/>
-      <c r="D187" s="3" t="n"/>
-      <c r="E187" s="3" t="n"/>
-      <c r="F187" s="3" t="n"/>
-      <c r="G187" s="3" t="n"/>
+      <c r="B187" s="4" t="inlineStr"/>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>capex_capitalisation_rate</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>Fraction of CapEx capitalised as PPE (IAS 16)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
-      <c r="A188" s="38" t="inlineStr">
-        <is>
-          <t>🏦 Terminal Valuation</t>
-        </is>
-      </c>
-      <c r="B188" s="3" t="n"/>
-      <c r="C188" s="3" t="n"/>
-      <c r="D188" s="3" t="n"/>
-      <c r="E188" s="3" t="n"/>
-      <c r="F188" s="3" t="n"/>
-      <c r="G188" s="3" t="n"/>
+      <c r="A188" s="8" t="inlineStr">
+        <is>
+          <t>Balance Sheet Accounting</t>
+        </is>
+      </c>
+      <c r="B188" s="8" t="inlineStr"/>
+      <c r="C188" s="9" t="inlineStr">
+        <is>
+          <t>annual_depreciation_rate</t>
+        </is>
+      </c>
+      <c r="D188" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E188" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F188" s="8" t="inlineStr">
+        <is>
+          <t>%/yr</t>
+        </is>
+      </c>
+      <c r="G188" s="11" t="inlineStr">
+        <is>
+          <t>Straight-line annual depreciation rate</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>Terminal Valuation</t>
+          <t>Balance Sheet Accounting</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr"/>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>shares_outstanding</t>
+          <t>brand_base_per_bu</t>
         </is>
       </c>
       <c r="D189" s="6" t="n">
-        <v>100000000</v>
+        <v>6250000</v>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
@@ -6751,60 +6792,60 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>$</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>Total shares outstanding for per-share valuation</t>
+          <t>Brand valuation base per business unit</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="8" t="inlineStr">
         <is>
-          <t>Terminal Valuation</t>
+          <t>Balance Sheet Accounting</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr"/>
       <c r="C190" s="9" t="inlineStr">
         <is>
-          <t>ipo_price_per_share</t>
+          <t>min_environmental_provision</t>
         </is>
       </c>
       <c r="D190" s="10" t="n">
-        <v>50</v>
+        <v>1000000</v>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F190" s="8" t="inlineStr">
         <is>
-          <t>$/share</t>
+          <t>$</t>
         </is>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
-          <t>IPO price per share (starting share price)</t>
+          <t>Minimum irreducible environmental provision (IAS 37)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>Terminal Valuation</t>
+          <t>Balance Sheet Accounting</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr"/>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>long_run_growth</t>
+          <t>decommissioning_accretion_rate</t>
         </is>
       </c>
       <c r="D191" s="6" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
@@ -6818,40 +6859,22 @@
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>Long-run perpetuity growth rate for DCF terminal value</t>
+          <t>Decommissioning provision accretion rate (IAS 37)</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="8" t="inlineStr">
-        <is>
-          <t>Terminal Valuation</t>
-        </is>
-      </c>
-      <c r="B192" s="8" t="inlineStr"/>
-      <c r="C192" s="9" t="inlineStr">
-        <is>
-          <t>exit_multiple_floor</t>
-        </is>
-      </c>
-      <c r="D192" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E192" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F192" s="8" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G192" s="11" t="inlineStr">
-        <is>
-          <t>Minimum exit EV/EBITDA multiple</t>
-        </is>
-      </c>
+      <c r="A192" s="23" t="inlineStr">
+        <is>
+          <t>🏦 Terminal Valuation</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="n"/>
+      <c r="C192" s="3" t="n"/>
+      <c r="D192" s="3" t="n"/>
+      <c r="E192" s="3" t="n"/>
+      <c r="F192" s="3" t="n"/>
+      <c r="G192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -6859,625 +6882,1001 @@
           <t>Terminal Valuation</t>
         </is>
       </c>
-      <c r="B193" s="3" t="n"/>
-      <c r="C193" s="3" t="n"/>
-      <c r="D193" s="3" t="n"/>
-      <c r="E193" s="3" t="n"/>
-      <c r="F193" s="3" t="n"/>
-      <c r="G193" s="3" t="n"/>
+      <c r="B193" s="4" t="inlineStr"/>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>shares_outstanding</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>Total shares outstanding for per-share valuation</t>
+        </is>
+      </c>
     </row>
     <row r="194">
-      <c r="A194" s="39" t="inlineStr">
-        <is>
-          <t>🦢 Black Swan Limits</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="n"/>
-      <c r="C194" s="3" t="n"/>
-      <c r="D194" s="3" t="n"/>
-      <c r="E194" s="3" t="n"/>
-      <c r="F194" s="3" t="n"/>
-      <c r="G194" s="3" t="n"/>
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t>Terminal Valuation</t>
+        </is>
+      </c>
+      <c r="B194" s="8" t="inlineStr"/>
+      <c r="C194" s="9" t="inlineStr">
+        <is>
+          <t>ipo_price_per_share</t>
+        </is>
+      </c>
+      <c r="D194" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E194" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="inlineStr">
+        <is>
+          <t>$/share</t>
+        </is>
+      </c>
+      <c r="G194" s="11" t="inlineStr">
+        <is>
+          <t>IPO price per share (starting share price)</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>Black Swan Limits</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="n"/>
-      <c r="C195" s="3" t="n"/>
-      <c r="D195" s="3" t="n"/>
-      <c r="E195" s="3" t="n"/>
-      <c r="F195" s="3" t="n"/>
-      <c r="G195" s="3" t="n"/>
+          <t>Terminal Valuation</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr"/>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>long_run_growth</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>%/yr</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>Long-run perpetuity growth rate for DCF terminal value</t>
+        </is>
+      </c>
     </row>
     <row r="196">
-      <c r="A196" s="40" t="inlineStr">
-        <is>
-          <t>🔄 Turnaround Pathway</t>
-        </is>
-      </c>
-      <c r="B196" s="3" t="n"/>
-      <c r="C196" s="3" t="n"/>
-      <c r="D196" s="3" t="n"/>
-      <c r="E196" s="3" t="n"/>
-      <c r="F196" s="3" t="n"/>
-      <c r="G196" s="3" t="n"/>
+      <c r="A196" s="8" t="inlineStr">
+        <is>
+          <t>Terminal Valuation</t>
+        </is>
+      </c>
+      <c r="B196" s="8" t="inlineStr"/>
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>exit_multiple_floor</t>
+        </is>
+      </c>
+      <c r="D196" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E196" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F196" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="G196" s="11" t="inlineStr">
+        <is>
+          <t>Minimum exit EV/EBITDA multiple</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>Turnaround Pathway</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>crisis</t>
-        </is>
-      </c>
+          <t>Terminal Valuation</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr"/>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>entry_treasury</t>
+          <t>exit_multiple_ceiling</t>
         </is>
       </c>
       <c r="D197" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>Treasury at or below this → crisis phase entry</t>
+          <t>Maximum exit EV/EBITDA multiple</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="8" t="inlineStr">
         <is>
-          <t>Turnaround Pathway</t>
+          <t>Terminal Valuation</t>
         </is>
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>pathway_difficulty</t>
         </is>
       </c>
       <c r="C198" s="9" t="inlineStr">
         <is>
-          <t>entry_reputation</t>
+          <t>activist_ultimatum</t>
         </is>
       </c>
       <c r="D198" s="10" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F198" s="8" t="inlineStr">
-        <is>
-          <t>pts</t>
-        </is>
-      </c>
-      <c r="G198" s="11" t="inlineStr">
-        <is>
-          <t>Reputation at or below this → crisis phase entry</t>
-        </is>
-      </c>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F198" s="8" t="inlineStr"/>
+      <c r="G198" s="11" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>Turnaround Pathway</t>
+          <t>Terminal Valuation</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>pathway_difficulty</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>bailout</t>
+          <t>climate_black_swan</t>
         </is>
       </c>
       <c r="D199" s="6" t="n">
-        <v>3000000</v>
+        <v>1.15</v>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F199" s="4" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="G199" s="7" t="inlineStr">
-        <is>
-          <t>Emergency bailout amount on crisis entry</t>
-        </is>
-      </c>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr"/>
+      <c r="G199" s="7" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="8" t="inlineStr">
         <is>
-          <t>Turnaround Pathway</t>
+          <t>Terminal Valuation</t>
         </is>
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>pathway_difficulty</t>
         </is>
       </c>
       <c r="C200" s="9" t="inlineStr">
         <is>
-          <t>capex_cap</t>
+          <t>stakeholder_revolt</t>
         </is>
       </c>
       <c r="D200" s="10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F200" s="8" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G200" s="11" t="inlineStr">
-        <is>
-          <t>CapEx cap multiplier during crisis phase</t>
-        </is>
-      </c>
+      <c r="F200" s="8" t="inlineStr"/>
+      <c r="G200" s="11" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>Turnaround Pathway</t>
+          <t>Terminal Valuation</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>pathway_difficulty</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>mr_cap</t>
+          <t>hostile_takeover</t>
         </is>
       </c>
       <c r="D201" s="6" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F201" s="4" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G201" s="7" t="inlineStr">
-        <is>
-          <t>Market-relative performance cap during crisis</t>
-        </is>
-      </c>
+      <c r="F201" s="4" t="inlineStr"/>
+      <c r="G201" s="7" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="8" t="inlineStr">
         <is>
+          <t>Terminal Valuation</t>
+        </is>
+      </c>
+      <c r="B202" s="8" t="inlineStr">
+        <is>
+          <t>pathway_difficulty</t>
+        </is>
+      </c>
+      <c r="C202" s="9" t="inlineStr">
+        <is>
+          <t>regulatory_shutdown</t>
+        </is>
+      </c>
+      <c r="D202" s="10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E202" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F202" s="8" t="inlineStr"/>
+      <c r="G202" s="11" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="24" t="inlineStr">
+        <is>
+          <t>🦢 Black Swan Limits</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="n"/>
+      <c r="C203" s="3" t="n"/>
+      <c r="D203" s="3" t="n"/>
+      <c r="E203" s="3" t="n"/>
+      <c r="F203" s="3" t="n"/>
+      <c r="G203" s="3" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>Black Swan Limits</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr"/>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>max_event_probability</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F204" s="4" t="inlineStr">
+        <is>
+          <t>prob</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>Hard ceiling on any single black swan event probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="25" t="inlineStr">
+        <is>
+          <t>🔄 Turnaround Pathway</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="n"/>
+      <c r="C205" s="3" t="n"/>
+      <c r="D205" s="3" t="n"/>
+      <c r="E205" s="3" t="n"/>
+      <c r="F205" s="3" t="n"/>
+      <c r="G205" s="3" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
           <t>Turnaround Pathway</t>
         </is>
       </c>
-      <c r="B202" s="8" t="inlineStr">
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>crisis</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>entry_treasury</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>Treasury at or below this → crisis phase entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="8" t="inlineStr">
+        <is>
+          <t>Turnaround Pathway</t>
+        </is>
+      </c>
+      <c r="B207" s="8" t="inlineStr">
+        <is>
+          <t>crisis</t>
+        </is>
+      </c>
+      <c r="C207" s="9" t="inlineStr">
+        <is>
+          <t>entry_reputation</t>
+        </is>
+      </c>
+      <c r="D207" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E207" s="8" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F207" s="8" t="inlineStr">
+        <is>
+          <t>pts</t>
+        </is>
+      </c>
+      <c r="G207" s="11" t="inlineStr">
+        <is>
+          <t>Reputation at or below this → crisis phase entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>Turnaround Pathway</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>crisis</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>bailout</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F208" s="4" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>Emergency bailout amount on crisis entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="8" t="inlineStr">
+        <is>
+          <t>Turnaround Pathway</t>
+        </is>
+      </c>
+      <c r="B209" s="8" t="inlineStr">
+        <is>
+          <t>crisis</t>
+        </is>
+      </c>
+      <c r="C209" s="9" t="inlineStr">
+        <is>
+          <t>capex_cap</t>
+        </is>
+      </c>
+      <c r="D209" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F209" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="G209" s="11" t="inlineStr">
+        <is>
+          <t>CapEx cap multiplier during crisis phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>Turnaround Pathway</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>crisis</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>mr_cap</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>Market-relative performance cap during crisis</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="inlineStr">
+        <is>
+          <t>Turnaround Pathway</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
         <is>
           <t>stabilisation</t>
         </is>
       </c>
-      <c r="C202" s="9" t="inlineStr">
+      <c r="C211" s="9" t="inlineStr">
         <is>
           <t>exit_treasury</t>
         </is>
       </c>
-      <c r="D202" s="10" t="n">
+      <c r="D211" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E202" s="8" t="inlineStr">
+      <c r="E211" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F202" s="8" t="inlineStr">
+      <c r="F211" s="8" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="G202" s="11" t="inlineStr">
+      <c r="G211" s="11" t="inlineStr">
         <is>
           <t>Treasury above this → exit stabilisation phase</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="4" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
         <is>
           <t>Turnaround Pathway</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr">
+      <c r="B212" s="4" t="inlineStr">
         <is>
           <t>stabilisation</t>
         </is>
       </c>
-      <c r="C203" s="5" t="inlineStr">
+      <c r="C212" s="5" t="inlineStr">
         <is>
           <t>exit_reputation</t>
         </is>
       </c>
-      <c r="D203" s="6" t="n">
+      <c r="D212" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="E203" s="4" t="inlineStr">
+      <c r="E212" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F203" s="4" t="inlineStr">
+      <c r="F212" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G203" s="7" t="inlineStr">
+      <c r="G212" s="7" t="inlineStr">
         <is>
           <t>Reputation above this → exit stabilisation phase</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="8" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
         <is>
           <t>Turnaround Pathway</t>
         </is>
       </c>
-      <c r="B204" s="8" t="inlineStr">
+      <c r="B213" s="8" t="inlineStr">
         <is>
           <t>stabilisation</t>
         </is>
       </c>
-      <c r="C204" s="9" t="inlineStr">
+      <c r="C213" s="9" t="inlineStr">
         <is>
           <t>capex_cap</t>
         </is>
       </c>
-      <c r="D204" s="10" t="n">
+      <c r="D213" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E204" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F204" s="8" t="inlineStr">
+      <c r="E213" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F213" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G204" s="11" t="inlineStr">
+      <c r="G213" s="11" t="inlineStr">
         <is>
           <t>CapEx cap multiplier during stabilisation</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="4" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
         <is>
           <t>Turnaround Pathway</t>
         </is>
       </c>
-      <c r="B205" s="4" t="inlineStr">
+      <c r="B214" s="4" t="inlineStr">
         <is>
           <t>stabilisation</t>
         </is>
       </c>
-      <c r="C205" s="5" t="inlineStr">
+      <c r="C214" s="5" t="inlineStr">
         <is>
           <t>mr_cap</t>
         </is>
       </c>
-      <c r="D205" s="6" t="n">
+      <c r="D214" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="E205" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F205" s="4" t="inlineStr">
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F214" s="4" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G205" s="7" t="inlineStr">
+      <c r="G214" s="7" t="inlineStr">
         <is>
           <t>Market-relative cap during stabilisation</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="8" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="8" t="inlineStr">
         <is>
           <t>Turnaround Pathway</t>
         </is>
       </c>
-      <c r="B206" s="8" t="inlineStr">
+      <c r="B215" s="8" t="inlineStr">
         <is>
           <t>recovery</t>
         </is>
       </c>
-      <c r="C206" s="9" t="inlineStr">
+      <c r="C215" s="9" t="inlineStr">
         <is>
           <t>exit_treasury</t>
         </is>
       </c>
-      <c r="D206" s="10" t="n">
+      <c r="D215" s="10" t="n">
         <v>10000000</v>
       </c>
-      <c r="E206" s="8" t="inlineStr">
+      <c r="E215" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F206" s="8" t="inlineStr">
+      <c r="F215" s="8" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="G206" s="11" t="inlineStr">
+      <c r="G215" s="11" t="inlineStr">
         <is>
           <t>Treasury above this → exit recovery phase</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="4" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
         <is>
           <t>Turnaround Pathway</t>
         </is>
       </c>
-      <c r="B207" s="4" t="inlineStr">
+      <c r="B216" s="4" t="inlineStr">
         <is>
           <t>recovery</t>
         </is>
       </c>
-      <c r="C207" s="5" t="inlineStr">
+      <c r="C216" s="5" t="inlineStr">
         <is>
           <t>exit_reputation</t>
         </is>
       </c>
-      <c r="D207" s="6" t="n">
+      <c r="D216" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="E207" s="4" t="inlineStr">
+      <c r="E216" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F207" s="4" t="inlineStr">
+      <c r="F216" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G207" s="7" t="inlineStr">
+      <c r="G216" s="7" t="inlineStr">
         <is>
           <t>Reputation above this → exit recovery phase</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="8" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="8" t="inlineStr">
         <is>
           <t>Turnaround Pathway</t>
         </is>
       </c>
-      <c r="B208" s="8" t="inlineStr">
+      <c r="B217" s="8" t="inlineStr">
         <is>
           <t>recovery</t>
         </is>
       </c>
-      <c r="C208" s="9" t="inlineStr">
+      <c r="C217" s="9" t="inlineStr">
         <is>
           <t>capex_cap</t>
         </is>
       </c>
-      <c r="D208" s="10" t="n">
+      <c r="D217" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E208" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F208" s="8" t="inlineStr">
+      <c r="E217" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F217" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G208" s="11" t="inlineStr">
+      <c r="G217" s="11" t="inlineStr">
         <is>
           <t>CapEx cap multiplier during recovery</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="4" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
         <is>
           <t>Turnaround Pathway</t>
         </is>
       </c>
-      <c r="B209" s="4" t="inlineStr">
+      <c r="B218" s="4" t="inlineStr">
         <is>
           <t>recovery</t>
         </is>
       </c>
-      <c r="C209" s="5" t="inlineStr">
+      <c r="C218" s="5" t="inlineStr">
         <is>
           <t>mr_cap</t>
         </is>
       </c>
-      <c r="D209" s="6" t="n">
+      <c r="D218" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="E209" s="4" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F209" s="4" t="inlineStr">
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G209" s="7" t="inlineStr">
+      <c r="G218" s="7" t="inlineStr">
         <is>
           <t>Market-relative cap during recovery</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="8" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="8" t="inlineStr">
         <is>
           <t>Turnaround Pathway</t>
         </is>
       </c>
-      <c r="B210" s="8" t="inlineStr">
+      <c r="B219" s="8" t="inlineStr">
         <is>
           <t>exit</t>
         </is>
       </c>
-      <c r="C210" s="9" t="inlineStr">
+      <c r="C219" s="9" t="inlineStr">
         <is>
           <t>exit_treasury</t>
         </is>
       </c>
-      <c r="D210" s="10" t="n">
+      <c r="D219" s="10" t="n">
         <v>20000000</v>
       </c>
-      <c r="E210" s="8" t="inlineStr">
+      <c r="E219" s="8" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F210" s="8" t="inlineStr">
+      <c r="F219" s="8" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="G210" s="11" t="inlineStr">
+      <c r="G219" s="11" t="inlineStr">
         <is>
           <t>Treasury above this → exit turnaround entirely</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="4" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
         <is>
           <t>Turnaround Pathway</t>
         </is>
       </c>
-      <c r="B211" s="4" t="inlineStr">
+      <c r="B220" s="4" t="inlineStr">
         <is>
           <t>exit</t>
         </is>
       </c>
-      <c r="C211" s="5" t="inlineStr">
+      <c r="C220" s="5" t="inlineStr">
         <is>
           <t>exit_reputation</t>
         </is>
       </c>
-      <c r="D211" s="6" t="n">
+      <c r="D220" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="E211" s="4" t="inlineStr">
+      <c r="E220" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F211" s="4" t="inlineStr">
+      <c r="F220" s="4" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
       </c>
-      <c r="G211" s="7" t="inlineStr">
+      <c r="G220" s="7" t="inlineStr">
         <is>
           <t>Reputation above this → exit turnaround entirely</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="8" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
         <is>
           <t>Turnaround Pathway</t>
         </is>
       </c>
-      <c r="B212" s="8" t="inlineStr">
+      <c r="B221" s="8" t="inlineStr">
         <is>
           <t>exit</t>
         </is>
       </c>
-      <c r="C212" s="9" t="inlineStr">
+      <c r="C221" s="9" t="inlineStr">
         <is>
           <t>mr_bonus</t>
         </is>
       </c>
-      <c r="D212" s="10" t="n">
+      <c r="D221" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="E212" s="8" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F212" s="8" t="inlineStr">
+      <c r="E221" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F221" s="8" t="inlineStr">
         <is>
           <t>bonus</t>
         </is>
       </c>
-      <c r="G212" s="11" t="inlineStr">
+      <c r="G221" s="11" t="inlineStr">
         <is>
           <t>Market-relative bonus awarded on turnaround completion</t>
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>Turnaround Pathway</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>max_rounds</t>
+        </is>
+      </c>
+      <c r="D222" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F222" s="4" t="inlineStr"/>
+      <c r="G222" s="7" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t>Turnaround Pathway</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>eligibility_mr_threshold</t>
+        </is>
+      </c>
+      <c r="D223" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E223" s="8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F223" s="8" t="inlineStr"/>
+      <c r="G223" s="11" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>Turnaround Pathway</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>entry_bailout</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F224" s="4" t="inlineStr"/>
+      <c r="G224" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G245"/>
+  <autoFilter ref="A1:G258"/>
   <mergeCells count="15">
-    <mergeCell ref="A169:G169"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A193:G193"/>
-    <mergeCell ref="A181:G181"/>
+    <mergeCell ref="A203:G203"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A192:G192"/>
+    <mergeCell ref="A186:G186"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A187:G187"/>
-    <mergeCell ref="A195:G195"/>
+    <mergeCell ref="A205:G205"/>
+    <mergeCell ref="A174:G174"/>
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="A10:G10"/>

--- a/simulation_config.xlsx
+++ b/simulation_config.xlsx
@@ -6232,7 +6232,7 @@
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>Investment ratio at/above which SLO stops decaying (default 0.10)</t>
+          <t>BU's own investment ratio at/above which its SLO stops decaying (default 0.15)</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
-          <t>Investment ratio at/above which SLO grows mildly (default 0.25)</t>
+          <t>BU's own investment ratio at/above which its SLO grows mildly (default 0.20)</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>Investment ratio at/above which SLO grows fully (default 0.50)</t>
+          <t>BU's own investment ratio at/above which its SLO grows fully (default 0.30)</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>Minimum absolute per-BU CapEx that counts as invested (default 500,000)</t>
+          <t>Minimum absolute per-BU CapEx that counts as invested (default 100,000)</t>
         </is>
       </c>
     </row>

--- a/simulation_config.xlsx
+++ b/simulation_config.xlsx
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>Min investment ratio to back a green claim credibly</t>
+          <t>Team share of the CSF pool that backs a full green claim (C-1: sum of BU ratios, not their average)</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>Scaling for moderate greenwash threshold</t>
+          <t>Scaling of the pool-share bar for a moderate green claim (0.67 → ≈10 %)</t>
         </is>
       </c>
     </row>
